--- a/data/processed/harmonization/Carbon__Water-extractable_organic_carbon/10.15485_1785525/10.15485_1785525_soil_Carbon__Water-extractable_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Water-extractable_organic_carbon/10.15485_1785525/10.15485_1785525_soil_Carbon__Water-extractable_organic_carbon.xlsx
@@ -432,7 +432,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
